--- a/artfynd/S 8169-2021 artfynd.xlsx
+++ b/artfynd/S 8169-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110344796</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100271260</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98337847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71727274</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,8 +1283,20 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56970032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>